--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
@@ -7096,7 +7096,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7170,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251027_201343.xlsx
@@ -5030,7 +5030,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
